--- a/Employee_Reports_wi48/Joe Vergil Jr Calanza Dormitorio Q0556.xlsx
+++ b/Employee_Reports_wi48/Joe Vergil Jr Calanza Dormitorio Q0556.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-86</v>
+        <v>-89</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-89</v>
+        <v>-92</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-284</v>
+        <v>-287</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-273</v>
+        <v>-276</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1097,11 +1097,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1146,11 +1146,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1244,11 +1244,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1330,11 +1330,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
